--- a/excel_templates/仪表表.xlsx
+++ b/excel_templates/仪表表.xlsx
@@ -794,12 +794,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>lan</t>
+          <t>test</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13800138001.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-02-11 19:47:53</t>
+          <t>2026-02-25 17:22:33</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -831,7 +831,11 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>lan</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -871,7 +875,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>借出</t>
+          <t>在库</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -881,25 +885,13 @@
           <t>2026-02-11 12:58:19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>lan</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-02-11 13:52</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-02-12 13:52:38</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>否</t>

--- a/excel_templates/仪表表.xlsx
+++ b/excel_templates/仪表表.xlsx
@@ -794,12 +794,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>lan</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13986903203</t>
+          <t>13800138001</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-02-25 17:22:33</t>
+          <t>2026-02-26 11:27:10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -831,11 +831,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>lan</t>
-        </is>
-      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
